--- a/data/satisfaction_detail/2026/1-6月/专业观众.xlsx
+++ b/data/satisfaction_detail/2026/1-6月/专业观众.xlsx
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>9.34</v>
+        <v>9.35</v>
       </c>
       <c r="C8" s="3" t="n">
         <v>9.890000000000001</v>
@@ -563,10 +563,10 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>9.16</v>
+        <v>9.18</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>9.84</v>
+        <v>9.83</v>
       </c>
     </row>
     <row r="10">
@@ -576,10 +576,10 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>9.07</v>
+        <v>9.08</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>9.869999999999999</v>
+        <v>9.880000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -602,10 +602,10 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>9.23</v>
+        <v>9.24</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>9.91</v>
+        <v>9.92</v>
       </c>
     </row>
     <row r="13">
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>9.140000000000001</v>
+        <v>9.16</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>9.85</v>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>9.880000000000001</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>9.98</v>
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>9.52</v>
+        <v>9.51</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>9.83</v>
@@ -667,10 +667,10 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>8.84</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>9.9</v>
+        <v>9.92</v>
       </c>
     </row>
     <row r="18">
